--- a/docs/视频主题清单.xlsx
+++ b/docs/视频主题清单.xlsx
@@ -13,7 +13,7 @@
     <sheet name="说明" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">主题清单!$A$1:$N$62</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">主题清单!$A$1:$N$69</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="429">
   <si>
     <t xml:space="preserve">类型</t>
   </si>
@@ -4719,6 +4719,176 @@
     <t xml:space="preserve">做减法，是最快的加法</t>
   </si>
   <si>
+    <t xml:space="preserve">E6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">学习时，手机放哪？</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Ward </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">等（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2017</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）近 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">800 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人实验：手机放在另一个房间的人测试表现最好，放桌上最差，即使静音朝下</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">学习的时候，让手机离开房间</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">批</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号男声</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E6_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">学习时手机放哪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">F1</t>
   </si>
   <si>
@@ -5162,25 +5332,6 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">号男声</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
       <t xml:space="preserve">F2_</t>
     </r>
     <r>
@@ -5336,6 +5487,181 @@
     <t xml:space="preserve">错题不是失败，是你的梯度</t>
   </si>
   <si>
+    <t xml:space="preserve">F6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新学期目标，拆小了才能完成</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bandura &amp; Schunk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1981</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">42 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">页数学练习，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">每次 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">页</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的小目标组进步最快、最有信心</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">大目标定方向，小目标给动力</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F6_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">新学期目标拆小了才能完成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">G1</t>
   </si>
   <si>
@@ -6452,6 +6778,85 @@
     <t xml:space="preserve">高三</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">I4_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">最后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">I5</t>
   </si>
   <si>
@@ -6488,6 +6893,357 @@
     <t xml:space="preserve">每个阶段，都有它该做的事</t>
   </si>
   <si>
+    <t xml:space="preserve">I6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">开学前，先把生物钟拨回来</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">寒假与上学作息差 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">小时；倒时差经验每天约调 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">小时 → 至少提前 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天开始</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">先把生物钟，拨回开学模式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">晨光</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">I6_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">开学前先把生物钟拨回来</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">I7</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">新学期，其实只有 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= 90 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天课；第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周期中；晚 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周进入状态就少 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">新学期，从第一周开始算数</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">I7_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">新学期其实只有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">J1</t>
   </si>
   <si>
@@ -7182,16 +7938,167 @@
     <t xml:space="preserve">支持要和孩子同频，才有用</t>
   </si>
   <si>
+    <t xml:space="preserve">纸雕</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">K3_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同频才能放大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">K4</t>
   </si>
   <si>
-    <t xml:space="preserve">风筝的线</t>
-  </si>
-  <si>
-    <t xml:space="preserve">风筝受力分析：线太紧会断，太松会坠</t>
-  </si>
-  <si>
-    <t xml:space="preserve">托举，不是攥紧</t>
+    <t xml:space="preserve">别把孩子的弹簧拉坏了</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">胡克定律 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F = kx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（弹性限度内）；超过弹性限度发生塑性形变，撤去外力回不到原长</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">给压力，也要给孩子留弹性</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">K4_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">别把孩子的弹簧拉坏了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">K5</t>
@@ -7206,6 +8113,363 @@
     <t xml:space="preserve">选对帮助，比给更多帮助重要</t>
   </si>
   <si>
+    <t xml:space="preserve">K6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">孩子每天该睡几个小时？</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">教育部（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2021</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：高中生每天睡眠应达 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">小时；只睡 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">小时一周欠 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">小时；睡眠中记忆巩固</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">睡够了，学进去的才留得住</t>
+  </si>
+  <si>
+    <t xml:space="preserve">流光渐变</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">K6_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">孩子每天该睡几个小时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">K7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">夸孩子聪明，还是夸努力？</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mueller &amp; Dweck</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1998</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：被夸聪明的孩子更多选简单题、受挫易放弃；被夸努力的更多选难题</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">少夸你真聪明，多夸你真努力</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">K7_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">夸孩子聪明还是夸努力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">K8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">孩子不听你说什么，看你做什么</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">班杜拉波波玩偶实验（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1961</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：儿童模仿成人行为（观察学习）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">最好的教育，是做给孩子看</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">K8_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">孩子看你做什么</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">L1</t>
   </si>
   <si>
@@ -7262,9 +8526,6 @@
     <t xml:space="preserve">考前学生</t>
   </si>
   <si>
-    <t xml:space="preserve">流光渐变</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -7633,6 +8894,23 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">68 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个主题（原规划 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">61 </t>
     </r>
     <r>
@@ -7641,7 +8919,75 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">个主题。每个主题都以一个真实的科学事实或算出来的数字作锚点，前 </t>
+      <t xml:space="preserve">个 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">批新增 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">K4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">换题）。每个主题都以一个真实的科学事实或算出来的数字作锚点，前 </t>
     </r>
     <r>
       <rPr>
@@ -8737,11 +10083,11 @@
         <v>12</v>
       </c>
       <c r="F2" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$62,A2)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$69,A2)</f>
         <v>6</v>
       </c>
       <c r="G2" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$62,A2,主题清单!$J$2:$J$62,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$69,A2,主题清单!$J$2:$J$69,"已制作")</f>
         <v>2</v>
       </c>
       <c r="H2" s="2" t="n">
@@ -8766,11 +10112,11 @@
         <v>17</v>
       </c>
       <c r="F3" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$62,A3)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$69,A3)</f>
         <v>6</v>
       </c>
       <c r="G3" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$62,A3,主题清单!$J$2:$J$62,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$69,A3,主题清单!$J$2:$J$69,"已制作")</f>
         <v>2</v>
       </c>
       <c r="H3" s="2" t="n">
@@ -8795,11 +10141,11 @@
         <v>21</v>
       </c>
       <c r="F4" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$62,A4)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$69,A4)</f>
         <v>6</v>
       </c>
       <c r="G4" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$62,A4,主题清单!$J$2:$J$62,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$69,A4,主题清单!$J$2:$J$69,"已制作")</f>
         <v>4</v>
       </c>
       <c r="H4" s="2" t="n">
@@ -8824,11 +10170,11 @@
         <v>24</v>
       </c>
       <c r="F5" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$62,A5)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$69,A5)</f>
         <v>5</v>
       </c>
       <c r="G5" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$62,A5,主题清单!$J$2:$J$62,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$69,A5,主题清单!$J$2:$J$69,"已制作")</f>
         <v>1</v>
       </c>
       <c r="H5" s="2" t="n">
@@ -8853,12 +10199,12 @@
         <v>28</v>
       </c>
       <c r="F6" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$62,A6)</f>
-        <v>5</v>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$69,A6)</f>
+        <v>6</v>
       </c>
       <c r="G6" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$62,A6,主题清单!$J$2:$J$62,"已制作")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$69,A6,主题清单!$J$2:$J$69,"已制作")</f>
+        <v>2</v>
       </c>
       <c r="H6" s="2" t="n">
         <f aca="false">F6-G6</f>
@@ -8882,12 +10228,12 @@
         <v>32</v>
       </c>
       <c r="F7" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$62,A7)</f>
-        <v>5</v>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$69,A7)</f>
+        <v>6</v>
       </c>
       <c r="G7" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$62,A7,主题清单!$J$2:$J$62,"已制作")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$69,A7,主题清单!$J$2:$J$69,"已制作")</f>
+        <v>3</v>
       </c>
       <c r="H7" s="2" t="n">
         <f aca="false">F7-G7</f>
@@ -8911,11 +10257,11 @@
         <v>35</v>
       </c>
       <c r="F8" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$62,A8)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$69,A8)</f>
         <v>5</v>
       </c>
       <c r="G8" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$62,A8,主题清单!$J$2:$J$62,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$69,A8,主题清单!$J$2:$J$69,"已制作")</f>
         <v>3</v>
       </c>
       <c r="H8" s="2" t="n">
@@ -8940,11 +10286,11 @@
         <v>38</v>
       </c>
       <c r="F9" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$62,A9)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$69,A9)</f>
         <v>4</v>
       </c>
       <c r="G9" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$62,A9,主题清单!$J$2:$J$62,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$69,A9,主题清单!$J$2:$J$69,"已制作")</f>
         <v>1</v>
       </c>
       <c r="H9" s="2" t="n">
@@ -8969,16 +10315,16 @@
         <v>41</v>
       </c>
       <c r="F10" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$62,A10)</f>
-        <v>5</v>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$69,A10)</f>
+        <v>7</v>
       </c>
       <c r="G10" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$62,A10,主题清单!$J$2:$J$62,"已制作")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$69,A10,主题清单!$J$2:$J$69,"已制作")</f>
+        <v>4</v>
       </c>
       <c r="H10" s="2" t="n">
         <f aca="false">F10-G10</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8998,11 +10344,11 @@
         <v>45</v>
       </c>
       <c r="F11" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$62,A11)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$69,A11)</f>
         <v>5</v>
       </c>
       <c r="G11" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$62,A11,主题清单!$J$2:$J$62,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$69,A11,主题清单!$J$2:$J$69,"已制作")</f>
         <v>2</v>
       </c>
       <c r="H11" s="2" t="n">
@@ -9027,16 +10373,16 @@
         <v>49</v>
       </c>
       <c r="F12" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$62,A12)</f>
-        <v>5</v>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$69,A12)</f>
+        <v>8</v>
       </c>
       <c r="G12" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$62,A12,主题清单!$J$2:$J$62,"已制作")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$69,A12,主题清单!$J$2:$J$69,"已制作")</f>
+        <v>7</v>
       </c>
       <c r="H12" s="2" t="n">
         <f aca="false">F12-G12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9056,11 +10402,11 @@
         <v>53</v>
       </c>
       <c r="F13" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$62,A13)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$69,A13)</f>
         <v>4</v>
       </c>
       <c r="G13" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$62,A13,主题清单!$J$2:$J$62,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$69,A13,主题清单!$J$2:$J$69,"已制作")</f>
         <v>2</v>
       </c>
       <c r="H13" s="2" t="n">
@@ -9074,15 +10420,15 @@
       </c>
       <c r="F14" s="8" t="n">
         <f aca="false">SUM(F2:F13)</f>
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G14" s="8" t="n">
         <f aca="false">SUM(G2:G13)</f>
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="H14" s="8" t="n">
         <f aca="false">SUM(H2:H13)</f>
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9091,7 +10437,7 @@
       </c>
       <c r="G15" s="9" t="n">
         <f aca="false">IF(F14=0,0,G14/F14)</f>
-        <v>0.377049180327869</v>
+        <v>0.485294117647059</v>
       </c>
     </row>
   </sheetData>
@@ -9110,7 +10456,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:N69"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -10229,7 +11575,7 @@
         <v>215</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>26</v>
@@ -10237,7 +11583,7 @@
       <c r="D30" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="10" t="s">
         <v>217</v>
       </c>
       <c r="F30" s="11" t="s">
@@ -10249,17 +11595,15 @@
       <c r="H30" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I30" s="10" t="s">
-        <v>74</v>
-      </c>
+      <c r="I30" s="10"/>
       <c r="J30" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>75</v>
+        <v>219</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>219</v>
+        <v>76</v>
       </c>
       <c r="M30" s="10" t="s">
         <v>220</v>
@@ -10303,52 +11647,62 @@
         <v>75</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>110</v>
+        <v>226</v>
       </c>
       <c r="M31" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B32" s="2" t="s">
+      <c r="A32" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="B32" s="10" t="s">
         <v>29</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="E32" s="4" t="s">
+      <c r="D32" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="E32" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="G32" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I32" s="2"/>
-      <c r="J32" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
-      <c r="N32" s="2"/>
+      <c r="F32" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="L32" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="M32" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="N32" s="10" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>29</v>
@@ -10357,19 +11711,19 @@
         <v>26</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="I33" s="2"/>
       <c r="J33" s="4" t="s">
@@ -10382,7 +11736,7 @@
     </row>
     <row r="34" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>29</v>
@@ -10390,17 +11744,17 @@
       <c r="C34" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>237</v>
+      <c r="D34" s="4" t="s">
+        <v>239</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>73</v>
@@ -10415,231 +11769,229 @@
       <c r="N34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="E35" s="11" t="s">
+      <c r="A35" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="F35" s="11" t="s">
+      <c r="B35" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="G35" s="11" t="s">
+      <c r="E35" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="H35" s="10" t="s">
+      <c r="F35" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I35" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="J35" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="K35" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="L35" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="M35" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="N35" s="10" t="s">
-        <v>245</v>
-      </c>
+      <c r="I35" s="2"/>
+      <c r="J35" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
         <v>246</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>9</v>
+        <v>29</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E36" s="10" t="s">
         <v>248</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>249</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>74</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="I36" s="10"/>
       <c r="J36" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K36" s="11" t="s">
-        <v>109</v>
+        <v>219</v>
       </c>
       <c r="L36" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="M36" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="N36" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="M36" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="N36" s="10" t="s">
+    </row>
+    <row r="37" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="10" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="10" t="s">
         <v>33</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="E37" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="F37" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="G37" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="G37" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H37" s="2" t="s">
+      <c r="H37" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I37" s="2"/>
-      <c r="J37" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
-      <c r="N37" s="2"/>
+      <c r="I37" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="L37" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="M37" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="N37" s="10" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="B38" s="2" t="s">
+      <c r="A38" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="B38" s="10" t="s">
         <v>33</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D38" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="E38" s="4" t="s">
+      <c r="D38" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="E38" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="G38" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H38" s="2" t="s">
+      <c r="F38" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="G38" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="H38" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="I38" s="2"/>
-      <c r="J38" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
+      <c r="I38" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="M38" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="N38" s="10" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="B39" s="10" t="s">
+      <c r="A39" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D39" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="G39" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="I39" s="10"/>
-      <c r="J39" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="K39" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="L39" s="11" t="s">
+      <c r="D39" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="M39" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="N39" s="10" t="s">
+      <c r="E39" s="2" t="s">
         <v>265</v>
       </c>
+      <c r="F39" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I39" s="2"/>
+      <c r="J39" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="F40" s="4" t="s">
         <v>269</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>270</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>48</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>74</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="I40" s="2"/>
       <c r="J40" s="4" t="s">
         <v>7</v>
       </c>
@@ -10648,53 +12000,51 @@
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
     </row>
-    <row r="41" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G41" s="11" t="s">
         <v>201</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="I41" s="10" t="s">
-        <v>74</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="I41" s="10"/>
       <c r="J41" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="L41" s="11" t="s">
-        <v>162</v>
+        <v>275</v>
       </c>
       <c r="M41" s="10" t="s">
-        <v>152</v>
+        <v>220</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>36</v>
@@ -10703,21 +12053,23 @@
         <v>9</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>48</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I42" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="J42" s="4" t="s">
         <v>7</v>
       </c>
@@ -10726,108 +12078,108 @@
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="B43" s="2" t="s">
+    <row r="43" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="B43" s="10" t="s">
         <v>36</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D43" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="F43" s="4" t="s">
+      <c r="D43" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="G43" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I43" s="2"/>
-      <c r="J43" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K43" s="2"/>
-      <c r="L43" s="2"/>
-      <c r="M43" s="2"/>
-      <c r="N43" s="2"/>
+      <c r="E43" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="L43" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="M43" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="N43" s="10" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="44" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>39</v>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D44" s="11" t="s">
-        <v>284</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>286</v>
-      </c>
-      <c r="G44" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H44" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="I44" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="J44" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="K44" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="L44" s="11" t="s">
+      <c r="D44" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="M44" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="N44" s="10" t="s">
+      <c r="E44" s="4" t="s">
         <v>288</v>
       </c>
+      <c r="F44" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I44" s="2"/>
+      <c r="J44" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+      <c r="N44" s="2"/>
     </row>
-    <row r="45" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>293</v>
+        <v>20</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="I45" s="2"/>
       <c r="J45" s="4" t="s">
@@ -10838,43 +12190,53 @@
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="s">
+    <row r="46" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="G46" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I46" s="2"/>
-      <c r="J46" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
-      <c r="N46" s="2"/>
+      <c r="G46" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="M46" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="N46" s="10" t="s">
+        <v>299</v>
+      </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -10883,19 +12245,19 @@
         <v>9</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>302</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="I47" s="2"/>
       <c r="J47" s="4" t="s">
@@ -10908,7 +12270,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>39</v>
@@ -10917,16 +12279,16 @@
         <v>9</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>84</v>
@@ -10940,78 +12302,74 @@
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
     </row>
-    <row r="49" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>26</v>
+        <v>39</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>308</v>
-      </c>
-      <c r="E49" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>311</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="I49" s="10" t="s">
-        <v>74</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="I49" s="10"/>
       <c r="J49" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K49" s="11" t="s">
-        <v>75</v>
+        <v>219</v>
       </c>
       <c r="L49" s="11" t="s">
-        <v>250</v>
+        <v>86</v>
       </c>
       <c r="M49" s="10" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>26</v>
+        <v>39</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="I50" s="2" t="s">
-        <v>74</v>
-      </c>
+      <c r="I50" s="2"/>
       <c r="J50" s="4" t="s">
         <v>7</v>
       </c>
@@ -11022,186 +12380,194 @@
     </row>
     <row r="51" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>26</v>
+        <v>39</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K51" s="11" t="s">
-        <v>109</v>
+        <v>219</v>
       </c>
       <c r="L51" s="11" t="s">
-        <v>76</v>
+        <v>323</v>
       </c>
       <c r="M51" s="10" t="s">
-        <v>226</v>
+        <v>77</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D52" s="4" t="s">
+      <c r="A52" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="G52" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H52" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="I52" s="10"/>
+      <c r="J52" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K52" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="L52" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="E52" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I52" s="2"/>
-      <c r="J52" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K52" s="2"/>
-      <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
-      <c r="N52" s="2"/>
+      <c r="M52" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="N52" s="10" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="B53" s="2" t="s">
+      <c r="A53" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="B53" s="10" t="s">
         <v>42</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D53" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I53" s="2"/>
-      <c r="J53" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K53" s="2"/>
-      <c r="L53" s="2"/>
-      <c r="M53" s="2"/>
-      <c r="N53" s="2"/>
+      <c r="D53" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="G53" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I53" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="L53" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="M53" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="N53" s="10" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="10" t="s">
-        <v>330</v>
-      </c>
-      <c r="B54" s="10" t="s">
-        <v>46</v>
+      <c r="A54" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D54" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="E54" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="F54" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="G54" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H54" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="I54" s="10" t="s">
+      <c r="D54" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I54" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J54" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="K54" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="L54" s="11" t="s">
-        <v>334</v>
-      </c>
-      <c r="M54" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="N54" s="10" t="s">
-        <v>335</v>
-      </c>
+      <c r="J54" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
+      <c r="M54" s="2"/>
+      <c r="N54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>26</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="H55" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="I55" s="10" t="s">
-        <v>74</v>
-      </c>
+      <c r="I55" s="10"/>
       <c r="J55" s="11" t="s">
         <v>6</v>
       </c>
@@ -11209,36 +12575,36 @@
         <v>109</v>
       </c>
       <c r="L55" s="11" t="s">
-        <v>334</v>
+        <v>76</v>
       </c>
       <c r="M55" s="10" t="s">
         <v>220</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>48</v>
+        <v>201</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>73</v>
@@ -11254,25 +12620,25 @@
     </row>
     <row r="57" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>26</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>84</v>
@@ -11287,60 +12653,70 @@
       <c r="N57" s="2"/>
     </row>
     <row r="58" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="B58" s="2" t="s">
+      <c r="A58" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="B58" s="10" t="s">
         <v>46</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D58" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="G58" s="4" t="s">
+      <c r="D58" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="E58" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="F58" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="G58" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H58" s="2" t="s">
+      <c r="H58" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I58" s="2"/>
-      <c r="J58" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K58" s="2"/>
-      <c r="L58" s="2"/>
-      <c r="M58" s="2"/>
-      <c r="N58" s="2"/>
+      <c r="I58" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="J58" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K58" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="L58" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="M58" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="N58" s="10" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="10" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>26</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>357</v>
+        <v>48</v>
       </c>
       <c r="H59" s="10" t="s">
         <v>84</v>
@@ -11355,117 +12731,123 @@
         <v>109</v>
       </c>
       <c r="L59" s="11" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="M59" s="10" t="s">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="H60" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I60" s="10" t="s">
-        <v>74</v>
-      </c>
+      <c r="I60" s="10"/>
       <c r="J60" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K60" s="11" t="s">
-        <v>109</v>
+        <v>219</v>
       </c>
       <c r="L60" s="11" t="s">
-        <v>117</v>
+        <v>368</v>
       </c>
       <c r="M60" s="10" t="s">
-        <v>77</v>
+        <v>227</v>
       </c>
       <c r="N60" s="10" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>50</v>
+      <c r="A61" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>46</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D61" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I61" s="2"/>
-      <c r="J61" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K61" s="2"/>
-      <c r="L61" s="2"/>
-      <c r="M61" s="2"/>
-      <c r="N61" s="2"/>
+      <c r="D61" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="F61" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="G61" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H61" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I61" s="10"/>
+      <c r="J61" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K61" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="L61" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="M61" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="N61" s="10" t="s">
+        <v>374</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>357</v>
+        <v>48</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="I62" s="2"/>
       <c r="J62" s="4" t="s">
@@ -11476,8 +12858,290 @@
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
     </row>
+    <row r="63" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="E63" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="F63" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="G63" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H63" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I63" s="10"/>
+      <c r="J63" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K63" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="L63" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="M63" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="N63" s="10" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="G64" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H64" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I64" s="10"/>
+      <c r="J64" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K64" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="L64" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="M64" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="N64" s="10" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="F65" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="G65" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H65" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I65" s="10"/>
+      <c r="J65" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K65" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="L65" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="M65" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="N65" s="10" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="E66" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="F66" s="11" t="s">
+        <v>398</v>
+      </c>
+      <c r="G66" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="H66" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="I66" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="J66" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K66" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="L66" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="M66" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="N66" s="10" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="F67" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="G67" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="H67" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I67" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="J67" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K67" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="L67" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="M67" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="N67" s="10" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I68" s="2"/>
+      <c r="J68" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2"/>
+    </row>
+    <row r="69" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I69" s="2"/>
+      <c r="J69" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K69" s="2"/>
+      <c r="L69" s="2"/>
+      <c r="M69" s="2"/>
+      <c r="N69" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N62"/>
+  <autoFilter ref="A1:N69"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -11503,10 +13167,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>374</v>
+        <v>415</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>375</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11514,7 +13178,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>376</v>
+        <v>417</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11522,7 +13186,7 @@
         <v>61</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11530,7 +13194,7 @@
         <v>62</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>378</v>
+        <v>419</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11538,39 +13202,39 @@
         <v>63</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>379</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>380</v>
+        <v>421</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>381</v>
+        <v>422</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>382</v>
+        <v>423</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>383</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>387</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>

--- a/docs/视频主题清单.xlsx
+++ b/docs/视频主题清单.xlsx
@@ -13,7 +13,7 @@
     <sheet name="说明" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">主题清单!$A$1:$N$69</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">主题清单!$A$1:$N$70</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="446">
   <si>
     <t xml:space="preserve">类型</t>
   </si>
@@ -3299,6 +3299,117 @@
     <t xml:space="preserve">差一点点和做到了，是两个世界</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">批</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">深空</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号男声</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C4_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">差一点就飞不出地球</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">C5</t>
   </si>
   <si>
@@ -4011,6 +4122,88 @@
     <t xml:space="preserve">每一次都只是翻倍，最后一次到了月球</t>
   </si>
   <si>
+    <t xml:space="preserve">纸雕</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D2_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">把纸对折</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">42</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">D3</t>
   </si>
   <si>
@@ -4146,6 +4339,90 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">手账笔记</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号女声</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D3_3000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个单词其实只要一年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">D4</t>
   </si>
   <si>
@@ -4264,6 +4541,71 @@
     <t xml:space="preserve">高二高三生</t>
   </si>
   <si>
+    <t xml:space="preserve">黑板粉笔</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D5_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">曲线下面的面积</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">E1</t>
   </si>
   <si>
@@ -4276,6 +4618,68 @@
     <t xml:space="preserve">不是你不够亮，是你太分散</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E1_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同样的阳光为什么能点燃纸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">E2</t>
   </si>
   <si>
@@ -4616,6 +5020,68 @@
     <t xml:space="preserve">写作业时回一条消息，代价比你想的大</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E4_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">边写作业边回消息代价有多大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">E5</t>
   </si>
   <si>
@@ -4815,25 +5281,6 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">号男声</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
       <t xml:space="preserve">E6_</t>
     </r>
     <r>
@@ -5120,28 +5567,6 @@
     <t xml:space="preserve">不是你记性差，是没在对的时间复习</t>
   </si>
   <si>
-    <t xml:space="preserve">手账笔记</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">号女声</t>
-    </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -5487,6 +5912,68 @@
     <t xml:space="preserve">错题不是失败，是你的梯度</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F5_AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">是靠犯错学会的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">F6</t>
   </si>
   <si>
@@ -5889,9 +6376,6 @@
     <t xml:space="preserve">原地踏步，就是后退</t>
   </si>
   <si>
-    <t xml:space="preserve">黑板粉笔</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -6331,6 +6815,71 @@
     <t xml:space="preserve">决定高度的，是最短的那块板</t>
   </si>
   <si>
+    <t xml:space="preserve">复古报纸</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H1_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">你的总分被哪一科拖住了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">H2</t>
   </si>
   <si>
@@ -7244,6 +7793,205 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">I8</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期中之后，还有 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周学期、第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周期中，后面还有 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周；错题分三类：不会 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">粗心 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">没时间</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">期中是半场，下半场才定输赢</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">I8_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期中之后还有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">J1</t>
   </si>
   <si>
@@ -7938,9 +8686,6 @@
     <t xml:space="preserve">支持要和孩子同频，才有用</t>
   </si>
   <si>
-    <t xml:space="preserve">纸雕</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -8782,6 +9527,68 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L3_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">一次考砸只是一个点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">L4</t>
   </si>
   <si>
@@ -8894,7 +9701,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">68 </t>
+      <t xml:space="preserve">69 </t>
     </r>
     <r>
       <rPr>
@@ -8963,6 +9770,57 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">批新增 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
     </r>
     <r>
       <rPr>
@@ -10083,11 +10941,11 @@
         <v>12</v>
       </c>
       <c r="F2" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$69,A2)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$70,A2)</f>
         <v>6</v>
       </c>
       <c r="G2" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$69,A2,主题清单!$J$2:$J$69,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$70,A2,主题清单!$J$2:$J$70,"已制作")</f>
         <v>2</v>
       </c>
       <c r="H2" s="2" t="n">
@@ -10112,11 +10970,11 @@
         <v>17</v>
       </c>
       <c r="F3" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$69,A3)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$70,A3)</f>
         <v>6</v>
       </c>
       <c r="G3" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$69,A3,主题清单!$J$2:$J$69,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$70,A3,主题清单!$J$2:$J$70,"已制作")</f>
         <v>2</v>
       </c>
       <c r="H3" s="2" t="n">
@@ -10141,16 +10999,16 @@
         <v>21</v>
       </c>
       <c r="F4" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$69,A4)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$70,A4)</f>
         <v>6</v>
       </c>
       <c r="G4" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$69,A4,主题清单!$J$2:$J$69,"已制作")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$70,A4,主题清单!$J$2:$J$70,"已制作")</f>
+        <v>5</v>
       </c>
       <c r="H4" s="2" t="n">
         <f aca="false">F4-G4</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10170,16 +11028,16 @@
         <v>24</v>
       </c>
       <c r="F5" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$69,A5)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$70,A5)</f>
         <v>5</v>
       </c>
       <c r="G5" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$69,A5,主题清单!$J$2:$J$69,"已制作")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$70,A5,主题清单!$J$2:$J$70,"已制作")</f>
+        <v>4</v>
       </c>
       <c r="H5" s="2" t="n">
         <f aca="false">F5-G5</f>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10199,16 +11057,16 @@
         <v>28</v>
       </c>
       <c r="F6" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$69,A6)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$70,A6)</f>
         <v>6</v>
       </c>
       <c r="G6" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$69,A6,主题清单!$J$2:$J$69,"已制作")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$70,A6,主题清单!$J$2:$J$70,"已制作")</f>
+        <v>4</v>
       </c>
       <c r="H6" s="2" t="n">
         <f aca="false">F6-G6</f>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10228,16 +11086,16 @@
         <v>32</v>
       </c>
       <c r="F7" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$69,A7)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$70,A7)</f>
         <v>6</v>
       </c>
       <c r="G7" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$69,A7,主题清单!$J$2:$J$69,"已制作")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$70,A7,主题清单!$J$2:$J$70,"已制作")</f>
+        <v>4</v>
       </c>
       <c r="H7" s="2" t="n">
         <f aca="false">F7-G7</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10257,11 +11115,11 @@
         <v>35</v>
       </c>
       <c r="F8" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$69,A8)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$70,A8)</f>
         <v>5</v>
       </c>
       <c r="G8" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$69,A8,主题清单!$J$2:$J$69,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$70,A8,主题清单!$J$2:$J$70,"已制作")</f>
         <v>3</v>
       </c>
       <c r="H8" s="2" t="n">
@@ -10286,16 +11144,16 @@
         <v>38</v>
       </c>
       <c r="F9" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$69,A9)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$70,A9)</f>
         <v>4</v>
       </c>
       <c r="G9" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$69,A9,主题清单!$J$2:$J$69,"已制作")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$70,A9,主题清单!$J$2:$J$70,"已制作")</f>
+        <v>2</v>
       </c>
       <c r="H9" s="2" t="n">
         <f aca="false">F9-G9</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10315,12 +11173,12 @@
         <v>41</v>
       </c>
       <c r="F10" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$69,A10)</f>
-        <v>7</v>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$70,A10)</f>
+        <v>8</v>
       </c>
       <c r="G10" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$69,A10,主题清单!$J$2:$J$69,"已制作")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$70,A10,主题清单!$J$2:$J$70,"已制作")</f>
+        <v>5</v>
       </c>
       <c r="H10" s="2" t="n">
         <f aca="false">F10-G10</f>
@@ -10344,11 +11202,11 @@
         <v>45</v>
       </c>
       <c r="F11" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$69,A11)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$70,A11)</f>
         <v>5</v>
       </c>
       <c r="G11" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$69,A11,主题清单!$J$2:$J$69,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$70,A11,主题清单!$J$2:$J$70,"已制作")</f>
         <v>2</v>
       </c>
       <c r="H11" s="2" t="n">
@@ -10373,11 +11231,11 @@
         <v>49</v>
       </c>
       <c r="F12" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$69,A12)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$70,A12)</f>
         <v>8</v>
       </c>
       <c r="G12" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$69,A12,主题清单!$J$2:$J$69,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$70,A12,主题清单!$J$2:$J$70,"已制作")</f>
         <v>7</v>
       </c>
       <c r="H12" s="2" t="n">
@@ -10402,16 +11260,16 @@
         <v>53</v>
       </c>
       <c r="F13" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$69,A13)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$70,A13)</f>
         <v>4</v>
       </c>
       <c r="G13" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$69,A13,主题清单!$J$2:$J$69,"已制作")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$70,A13,主题清单!$J$2:$J$70,"已制作")</f>
+        <v>3</v>
       </c>
       <c r="H13" s="2" t="n">
         <f aca="false">F13-G13</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10420,15 +11278,15 @@
       </c>
       <c r="F14" s="8" t="n">
         <f aca="false">SUM(F2:F13)</f>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G14" s="8" t="n">
         <f aca="false">SUM(G2:G13)</f>
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="H14" s="8" t="n">
         <f aca="false">SUM(H2:H13)</f>
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10437,7 +11295,7 @@
       </c>
       <c r="G15" s="9" t="n">
         <f aca="false">IF(F14=0,0,G14/F14)</f>
-        <v>0.485294117647059</v>
+        <v>0.623188405797101</v>
       </c>
     </row>
   </sheetData>
@@ -10456,7 +11314,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N69"/>
+  <dimension ref="A1:N70"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -11099,42 +11957,50 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="10" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I17" s="2"/>
-      <c r="J17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="M17" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="N17" s="10" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>18</v>
@@ -11143,13 +12009,13 @@
         <v>14</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>20</v>
@@ -11165,18 +12031,18 @@
         <v>109</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="N18" s="10" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>18</v>
@@ -11185,19 +12051,19 @@
         <v>14</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="4" t="s">
@@ -11210,7 +12076,7 @@
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>22</v>
@@ -11219,13 +12085,13 @@
         <v>14</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G20" s="11" t="s">
         <v>20</v>
@@ -11243,86 +12109,102 @@
         <v>75</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="A21" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="B21" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="G21" s="4" t="s">
+      <c r="D21" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="G21" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="I21" s="2"/>
-      <c r="J21" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="M21" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="N21" s="10" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B22" s="2" t="s">
+      <c r="A22" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="B22" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="D22" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="G22" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="H22" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="I22" s="2"/>
-      <c r="J22" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="M22" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="N22" s="10" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>22</v>
@@ -11331,13 +12213,13 @@
         <v>14</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>20</v>
@@ -11354,79 +12236,95 @@
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B24" s="2" t="s">
+    <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="H24" s="2" t="s">
+      <c r="D24" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H24" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I24" s="2"/>
-      <c r="J24" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="M24" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="N24" s="10" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B25" s="2" t="s">
+      <c r="A25" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="B25" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="G25" s="4" t="s">
+      <c r="D25" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="G25" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="I25" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="J25" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
+      <c r="J25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="M25" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="N25" s="10" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>25</v>
@@ -11435,16 +12333,16 @@
         <v>26</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="H26" s="10" t="s">
         <v>73</v>
@@ -11465,12 +12363,12 @@
         <v>77</v>
       </c>
       <c r="N26" s="10" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>25</v>
@@ -11479,13 +12377,13 @@
         <v>26</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>20</v>
@@ -11503,42 +12401,50 @@
       <c r="N27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B28" s="2" t="s">
+      <c r="A28" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="B28" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="G28" s="4" t="s">
+      <c r="D28" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="G28" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="H28" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="I28" s="2"/>
-      <c r="J28" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
-      <c r="N28" s="2"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="M28" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="N28" s="10" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>25</v>
@@ -11547,13 +12453,13 @@
         <v>26</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>48</v>
@@ -11572,7 +12478,7 @@
     </row>
     <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>25</v>
@@ -11581,13 +12487,13 @@
         <v>26</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="G30" s="11" t="s">
         <v>83</v>
@@ -11600,21 +12506,21 @@
         <v>6</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="L30" s="11" t="s">
         <v>76</v>
       </c>
       <c r="M30" s="10" t="s">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="N30" s="10" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>29</v>
@@ -11623,13 +12529,13 @@
         <v>26</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="G31" s="11" t="s">
         <v>83</v>
@@ -11647,18 +12553,18 @@
         <v>75</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>226</v>
+        <v>190</v>
       </c>
       <c r="M31" s="10" t="s">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>29</v>
@@ -11667,13 +12573,13 @@
         <v>26</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="G32" s="11" t="s">
         <v>83</v>
@@ -11694,15 +12600,15 @@
         <v>110</v>
       </c>
       <c r="M32" s="10" t="s">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="N32" s="10" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>29</v>
@@ -11711,13 +12617,13 @@
         <v>26</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>48</v>
@@ -11736,7 +12642,7 @@
     </row>
     <row r="34" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>29</v>
@@ -11745,13 +12651,13 @@
         <v>26</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>83</v>
@@ -11769,42 +12675,50 @@
       <c r="N34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="B35" s="2" t="s">
+      <c r="A35" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="B35" s="10" t="s">
         <v>29</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="G35" s="4" t="s">
+      <c r="D35" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="G35" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="H35" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I35" s="2"/>
-      <c r="J35" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2"/>
-      <c r="N35" s="2"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="L35" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="M35" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="N35" s="10" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>29</v>
@@ -11813,13 +12727,13 @@
         <v>26</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="G36" s="11" t="s">
         <v>20</v>
@@ -11832,21 +12746,21 @@
         <v>6</v>
       </c>
       <c r="K36" s="11" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="L36" s="11" t="s">
-        <v>226</v>
+        <v>190</v>
       </c>
       <c r="M36" s="10" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="N36" s="10" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>33</v>
@@ -11855,16 +12769,16 @@
         <v>9</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="H37" s="10" t="s">
         <v>73</v>
@@ -11885,12 +12799,12 @@
         <v>77</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>33</v>
@@ -11899,13 +12813,13 @@
         <v>9</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="G38" s="11" t="s">
         <v>83</v>
@@ -11923,18 +12837,18 @@
         <v>109</v>
       </c>
       <c r="L38" s="11" t="s">
-        <v>261</v>
+        <v>202</v>
       </c>
       <c r="M38" s="10" t="s">
         <v>111</v>
       </c>
       <c r="N38" s="10" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>33</v>
@@ -11943,13 +12857,13 @@
         <v>9</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>83</v>
@@ -11968,7 +12882,7 @@
     </row>
     <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>33</v>
@@ -11977,13 +12891,13 @@
         <v>9</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>48</v>
@@ -12002,7 +12916,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>33</v>
@@ -12011,16 +12925,16 @@
         <v>9</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="H41" s="10" t="s">
         <v>84</v>
@@ -12033,54 +12947,62 @@
         <v>109</v>
       </c>
       <c r="L41" s="11" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="M41" s="10" t="s">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="B42" s="2" t="s">
+      <c r="A42" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="B42" s="10" t="s">
         <v>36</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D42" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="G42" s="4" t="s">
+      <c r="D42" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="G42" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H42" s="2" t="s">
+      <c r="H42" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I42" s="2" t="s">
+      <c r="I42" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="J42" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K42" s="2"/>
-      <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
-      <c r="N42" s="2"/>
+      <c r="J42" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="L42" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="M42" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="N42" s="10" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>36</v>
@@ -12089,16 +13011,16 @@
         <v>9</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="H43" s="10" t="s">
         <v>73</v>
@@ -12113,18 +13035,18 @@
         <v>75</v>
       </c>
       <c r="L43" s="11" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="M43" s="10" t="s">
         <v>152</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>36</v>
@@ -12133,13 +13055,13 @@
         <v>9</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>48</v>
@@ -12158,7 +13080,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>36</v>
@@ -12167,13 +13089,13 @@
         <v>9</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>20</v>
@@ -12192,7 +13114,7 @@
     </row>
     <row r="46" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>39</v>
@@ -12201,16 +13123,16 @@
         <v>9</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="H46" s="10" t="s">
         <v>73</v>
@@ -12225,18 +13147,18 @@
         <v>109</v>
       </c>
       <c r="L46" s="11" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="M46" s="10" t="s">
         <v>152</v>
       </c>
       <c r="N46" s="10" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -12245,16 +13167,16 @@
         <v>9</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>73</v>
@@ -12270,7 +13192,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>39</v>
@@ -12279,13 +13201,13 @@
         <v>9</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>83</v>
@@ -12304,7 +13226,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>39</v>
@@ -12313,16 +13235,16 @@
         <v>9</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="H49" s="10" t="s">
         <v>84</v>
@@ -12332,7 +13254,7 @@
         <v>6</v>
       </c>
       <c r="K49" s="11" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="L49" s="11" t="s">
         <v>86</v>
@@ -12341,12 +13263,12 @@
         <v>77</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>39</v>
@@ -12355,13 +13277,13 @@
         <v>9</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>48</v>
@@ -12380,7 +13302,7 @@
     </row>
     <row r="51" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>39</v>
@@ -12389,13 +13311,13 @@
         <v>9</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G51" s="11" t="s">
         <v>83</v>
@@ -12408,21 +13330,21 @@
         <v>6</v>
       </c>
       <c r="K51" s="11" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="L51" s="11" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="M51" s="10" t="s">
         <v>77</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>39</v>
@@ -12431,13 +13353,13 @@
         <v>9</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="G52" s="11" t="s">
         <v>20</v>
@@ -12450,177 +13372,185 @@
         <v>6</v>
       </c>
       <c r="K52" s="11" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="L52" s="11" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="M52" s="10" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="N52" s="10" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>26</v>
+        <v>39</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="E53" s="11" t="s">
-        <v>332</v>
+        <v>343</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>344</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>334</v>
+        <v>20</v>
       </c>
       <c r="H53" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I53" s="10" t="s">
-        <v>74</v>
-      </c>
+      <c r="I53" s="10"/>
       <c r="J53" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K53" s="11" t="s">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="L53" s="11" t="s">
-        <v>261</v>
+        <v>335</v>
       </c>
       <c r="M53" s="10" t="s">
-        <v>111</v>
+        <v>191</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="B54" s="2" t="s">
+      <c r="A54" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="B54" s="10" t="s">
         <v>42</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D54" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I54" s="2" t="s">
+      <c r="D54" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="E54" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="H54" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I54" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="J54" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K54" s="2"/>
-      <c r="L54" s="2"/>
-      <c r="M54" s="2"/>
-      <c r="N54" s="2"/>
+      <c r="J54" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K54" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="L54" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="M54" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="N54" s="10" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="B55" s="10" t="s">
+      <c r="A55" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D55" s="11" t="s">
-        <v>341</v>
-      </c>
-      <c r="E55" s="11" t="s">
-        <v>342</v>
-      </c>
-      <c r="F55" s="11" t="s">
-        <v>343</v>
-      </c>
-      <c r="G55" s="11" t="s">
+      <c r="D55" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="G55" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H55" s="10" t="s">
+      <c r="H55" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="I55" s="10"/>
-      <c r="J55" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="K55" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="L55" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="M55" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="N55" s="10" t="s">
-        <v>344</v>
-      </c>
+      <c r="I55" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="B56" s="2" t="s">
+      <c r="A56" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="B56" s="10" t="s">
         <v>42</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D56" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I56" s="2"/>
-      <c r="J56" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K56" s="2"/>
-      <c r="L56" s="2"/>
-      <c r="M56" s="2"/>
-      <c r="N56" s="2"/>
+      <c r="D56" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="G56" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H56" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="I56" s="10"/>
+      <c r="J56" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K56" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="L56" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="M56" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="N56" s="10" t="s">
+        <v>361</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>42</v>
@@ -12629,19 +13559,19 @@
         <v>26</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>20</v>
+        <v>213</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="I57" s="2"/>
       <c r="J57" s="4" t="s">
@@ -12653,52 +13583,42 @@
       <c r="N57" s="2"/>
     </row>
     <row r="58" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="B58" s="10" t="s">
-        <v>46</v>
+      <c r="A58" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D58" s="11" t="s">
-        <v>354</v>
-      </c>
-      <c r="E58" s="11" t="s">
-        <v>355</v>
-      </c>
-      <c r="F58" s="11" t="s">
-        <v>356</v>
-      </c>
-      <c r="G58" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H58" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="I58" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="J58" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="K58" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="L58" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="M58" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="N58" s="10" t="s">
-        <v>358</v>
-      </c>
+      <c r="D58" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I58" s="2"/>
+      <c r="J58" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
+      <c r="M58" s="2"/>
+      <c r="N58" s="2"/>
     </row>
     <row r="59" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="10" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="B59" s="10" t="s">
         <v>46</v>
@@ -12707,19 +13627,19 @@
         <v>26</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="G59" s="11" t="s">
         <v>48</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="I59" s="10" t="s">
         <v>74</v>
@@ -12728,21 +13648,21 @@
         <v>6</v>
       </c>
       <c r="K59" s="11" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="L59" s="11" t="s">
-        <v>357</v>
+        <v>374</v>
       </c>
       <c r="M59" s="10" t="s">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="B60" s="10" t="s">
         <v>46</v>
@@ -12751,40 +13671,42 @@
         <v>26</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="G60" s="11" t="s">
         <v>48</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="I60" s="10"/>
+        <v>84</v>
+      </c>
+      <c r="I60" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="J60" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K60" s="11" t="s">
-        <v>219</v>
+        <v>109</v>
       </c>
       <c r="L60" s="11" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="M60" s="10" t="s">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="N60" s="10" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="10" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="B61" s="10" t="s">
         <v>46</v>
@@ -12793,13 +13715,13 @@
         <v>26</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="G61" s="11" t="s">
         <v>48</v>
@@ -12812,97 +13734,97 @@
         <v>6</v>
       </c>
       <c r="K61" s="11" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="L61" s="11" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="M61" s="10" t="s">
-        <v>111</v>
+        <v>191</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="B62" s="2" t="s">
+      <c r="A62" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="B62" s="10" t="s">
         <v>46</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D62" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="G62" s="4" t="s">
+      <c r="D62" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="F62" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="G62" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H62" s="2" t="s">
+      <c r="H62" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I62" s="2"/>
-      <c r="J62" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K62" s="2"/>
-      <c r="L62" s="2"/>
-      <c r="M62" s="2"/>
-      <c r="N62" s="2"/>
+      <c r="I62" s="10"/>
+      <c r="J62" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K62" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="L62" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="M62" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="N62" s="10" t="s">
+        <v>390</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="B63" s="10" t="s">
+      <c r="A63" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D63" s="11" t="s">
-        <v>380</v>
-      </c>
-      <c r="E63" s="11" t="s">
-        <v>381</v>
-      </c>
-      <c r="F63" s="11" t="s">
-        <v>382</v>
-      </c>
-      <c r="G63" s="11" t="s">
+      <c r="D63" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="G63" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H63" s="10" t="s">
+      <c r="H63" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I63" s="10"/>
-      <c r="J63" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="K63" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="L63" s="11" t="s">
-        <v>383</v>
-      </c>
-      <c r="M63" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="N63" s="10" t="s">
-        <v>384</v>
-      </c>
+      <c r="I63" s="2"/>
+      <c r="J63" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2"/>
     </row>
     <row r="64" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="B64" s="10" t="s">
         <v>46</v>
@@ -12911,13 +13833,13 @@
         <v>26</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>386</v>
-      </c>
-      <c r="E64" s="10" t="s">
-        <v>387</v>
+        <v>396</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>397</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="G64" s="11" t="s">
         <v>48</v>
@@ -12930,21 +13852,21 @@
         <v>6</v>
       </c>
       <c r="K64" s="11" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="L64" s="11" t="s">
-        <v>368</v>
+        <v>399</v>
       </c>
       <c r="M64" s="10" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="N64" s="10" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="B65" s="10" t="s">
         <v>46</v>
@@ -12953,13 +13875,13 @@
         <v>26</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>391</v>
-      </c>
-      <c r="E65" s="11" t="s">
-        <v>392</v>
+        <v>402</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>403</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="G65" s="11" t="s">
         <v>48</v>
@@ -12972,65 +13894,63 @@
         <v>6</v>
       </c>
       <c r="K65" s="11" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="L65" s="11" t="s">
-        <v>357</v>
+        <v>184</v>
       </c>
       <c r="M65" s="10" t="s">
-        <v>227</v>
+        <v>152</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="10" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="G66" s="11" t="s">
-        <v>399</v>
+        <v>48</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="I66" s="10" t="s">
-        <v>74</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="I66" s="10"/>
       <c r="J66" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K66" s="11" t="s">
-        <v>109</v>
+        <v>232</v>
       </c>
       <c r="L66" s="11" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="M66" s="10" t="s">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="N66" s="10" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="B67" s="10" t="s">
         <v>50</v>
@@ -13039,19 +13959,19 @@
         <v>26</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="G67" s="11" t="s">
-        <v>83</v>
+        <v>415</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="I67" s="10" t="s">
         <v>74</v>
@@ -13063,85 +13983,137 @@
         <v>109</v>
       </c>
       <c r="L67" s="11" t="s">
-        <v>117</v>
+        <v>399</v>
       </c>
       <c r="M67" s="10" t="s">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="B68" s="2" t="s">
+      <c r="A68" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="B68" s="10" t="s">
         <v>50</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D68" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I68" s="2"/>
-      <c r="J68" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K68" s="2"/>
-      <c r="L68" s="2"/>
-      <c r="M68" s="2"/>
-      <c r="N68" s="2"/>
+      <c r="D68" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>419</v>
+      </c>
+      <c r="F68" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="G68" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="H68" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I68" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="J68" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K68" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="L68" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="M68" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="N68" s="10" t="s">
+        <v>421</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="B69" s="2" t="s">
+      <c r="A69" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="B69" s="10" t="s">
         <v>50</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D69" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="E69" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="H69" s="2" t="s">
+      <c r="D69" s="11" t="s">
+        <v>423</v>
+      </c>
+      <c r="E69" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="F69" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="G69" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="I69" s="2"/>
-      <c r="J69" s="4" t="s">
+      <c r="I69" s="10"/>
+      <c r="J69" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K69" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="L69" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="M69" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="N69" s="10" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I70" s="2"/>
+      <c r="J70" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K69" s="2"/>
-      <c r="L69" s="2"/>
-      <c r="M69" s="2"/>
-      <c r="N69" s="2"/>
+      <c r="K70" s="2"/>
+      <c r="L70" s="2"/>
+      <c r="M70" s="2"/>
+      <c r="N70" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N69"/>
+  <autoFilter ref="A1:N70"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -13167,10 +14139,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13178,7 +14150,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>417</v>
+        <v>434</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13186,7 +14158,7 @@
         <v>61</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13194,7 +14166,7 @@
         <v>62</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>419</v>
+        <v>436</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13202,39 +14174,39 @@
         <v>63</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>423</v>
+        <v>440</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>424</v>
+        <v>441</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>426</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>427</v>
+        <v>444</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>428</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>

--- a/docs/视频主题清单.xlsx
+++ b/docs/视频主题清单.xlsx
@@ -13,7 +13,7 @@
     <sheet name="说明" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">主题清单!$A$1:$N$70</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">主题清单!$A$1:$N$80</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="532">
   <si>
     <t xml:space="preserve">类型</t>
   </si>
@@ -798,6 +798,83 @@
   </si>
   <si>
     <t xml:space="preserve">考前社群、考后安抚、主讲答疑会</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期末冲刺</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">最后几周，方法比时长更重要</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">学生（期末前 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">期末节点社群维护、促出勤、推冲刺课</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">N </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">寒假规划</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">寒假是一整块可支配时间，要会排、能完成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">寒假课推课、寒假规划讲座、家长群</t>
   </si>
   <si>
     <t xml:space="preserve">合计</t>
@@ -11784,6 +11861,1955 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">期末复习，多做题还是多看书？</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Roediger &amp; Karpicke</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2006</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：读 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">遍 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">读 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">遍 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">自测 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">遍——</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分钟后 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">83% vs 71%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周后 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40% vs 61%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">合上书，先考考自己</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">批</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M1_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期末复习多做题还是多看书</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">别按章节刷题，混着做</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rohrer &amp; Taylor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2007</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：练习时分块 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">89% vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">混合 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">60%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；一周后测验分块 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20% vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">混合 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">63%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">练的时候越顺，不一定学得越牢</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M2_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">别按章节刷题混着做</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">M3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期末最后 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周怎么排</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">复习安排建议：回归课本 → 专题补弱 → 限时套卷 → 查漏 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">调作息（非研究数据）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">冲刺不是拼命，是每周只盯一件事</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M3_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期末最后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周怎么排</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">M4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">考场卡住了，先跳过</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">新高考数学 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">I </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">卷 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">150 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ 120 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分钟 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= 1.25 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分钟；卡 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分钟 ≈ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">19 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分；单选 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8×5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、多选 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3×6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、填空 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3×5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、解答 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">77</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">期末拼的是会做的全拿到</t>
+  </si>
+  <si>
+    <t xml:space="preserve">试卷</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M4_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">考场卡住了先跳过</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">M5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">考前 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分钟，把担心写下来</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Ramirez &amp; Beilock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2011</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Science</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：考前写下担心 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分钟成绩更好，焦虑越高提升越明显</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">把担心写下来，把脑子留给考试</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M5_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">考前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分钟把担心写下来</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">N1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">寒假计划为什么总完不成</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Buehler </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">等（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1994</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）计划谬误：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">37 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名学生估计论文 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">33.9 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天，实际 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">55.5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天，按时完成约 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">计划留余量，才能真完成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">软木板</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">N1_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">寒假计划为什么总完不成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">N2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">寒假计划，写清几点、在哪</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Gollwitzer &amp; Brandstätter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1997</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）研究 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：圣诞假期难计划，写清何时何地完成 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">62%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，只写目标 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">写清楚：几点、在哪、做什么</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">N2_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">寒假计划写清几点在哪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">N3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">寒假 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天，按三段排</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027-01-23 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">放假、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天为例：春节 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日是第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天；年前 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">春节前后 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年后 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">寒假分三段，年前先发力</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">N3_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">寒假</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天按三段排</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">N4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">寒假在家，试试番茄钟</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">番茄工作法：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分钟专注 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ 5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分钟休息；一天 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= 3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">小时 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= 240 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">学习不看坐了多久，看专心了多久</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">N4_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">寒假在家试试番茄钟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">N5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">寒假预习：先做题，再看书</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Richland </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">等（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2009</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）预测试效应：学习前先尝试作答，即使答错也能促进后续学习</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">寒假预习，先做题，再看书</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">N5_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">寒假预习先做题再看书</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4 / _AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配音</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.mp4</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">用途</t>
   </si>
   <si>
@@ -11802,7 +13828,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">12 </t>
+      <t xml:space="preserve">14 </t>
     </r>
     <r>
       <rPr>
@@ -11819,7 +13845,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">69 </t>
+      <t xml:space="preserve">79 </t>
     </r>
     <r>
       <rPr>
@@ -11939,6 +13965,91 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">批新增「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期末冲刺」「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">N </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">寒假规划」两类各 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5 </t>
     </r>
     <r>
       <rPr>
@@ -13005,7 +15116,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
@@ -13059,11 +15170,11 @@
         <v>12</v>
       </c>
       <c r="F2" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$70,A2)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$80,A2)</f>
         <v>6</v>
       </c>
       <c r="G2" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$70,A2,主题清单!$J$2:$J$70,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$80,A2,主题清单!$J$2:$J$80,"已制作")</f>
         <v>5</v>
       </c>
       <c r="H2" s="2" t="n">
@@ -13088,11 +15199,11 @@
         <v>17</v>
       </c>
       <c r="F3" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$70,A3)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$80,A3)</f>
         <v>6</v>
       </c>
       <c r="G3" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$70,A3,主题清单!$J$2:$J$70,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$80,A3,主题清单!$J$2:$J$80,"已制作")</f>
         <v>6</v>
       </c>
       <c r="H3" s="2" t="n">
@@ -13117,11 +15228,11 @@
         <v>21</v>
       </c>
       <c r="F4" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$70,A4)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$80,A4)</f>
         <v>6</v>
       </c>
       <c r="G4" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$70,A4,主题清单!$J$2:$J$70,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$80,A4,主题清单!$J$2:$J$80,"已制作")</f>
         <v>6</v>
       </c>
       <c r="H4" s="2" t="n">
@@ -13146,11 +15257,11 @@
         <v>24</v>
       </c>
       <c r="F5" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$70,A5)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$80,A5)</f>
         <v>5</v>
       </c>
       <c r="G5" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$70,A5,主题清单!$J$2:$J$70,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$80,A5,主题清单!$J$2:$J$80,"已制作")</f>
         <v>5</v>
       </c>
       <c r="H5" s="2" t="n">
@@ -13175,11 +15286,11 @@
         <v>28</v>
       </c>
       <c r="F6" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$70,A6)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$80,A6)</f>
         <v>6</v>
       </c>
       <c r="G6" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$70,A6,主题清单!$J$2:$J$70,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$80,A6,主题清单!$J$2:$J$80,"已制作")</f>
         <v>5</v>
       </c>
       <c r="H6" s="2" t="n">
@@ -13204,11 +15315,11 @@
         <v>32</v>
       </c>
       <c r="F7" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$70,A7)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$80,A7)</f>
         <v>6</v>
       </c>
       <c r="G7" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$70,A7,主题清单!$J$2:$J$70,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$80,A7,主题清单!$J$2:$J$80,"已制作")</f>
         <v>6</v>
       </c>
       <c r="H7" s="2" t="n">
@@ -13233,11 +15344,11 @@
         <v>35</v>
       </c>
       <c r="F8" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$70,A8)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$80,A8)</f>
         <v>5</v>
       </c>
       <c r="G8" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$70,A8,主题清单!$J$2:$J$70,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$80,A8,主题清单!$J$2:$J$80,"已制作")</f>
         <v>4</v>
       </c>
       <c r="H8" s="2" t="n">
@@ -13262,11 +15373,11 @@
         <v>38</v>
       </c>
       <c r="F9" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$70,A9)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$80,A9)</f>
         <v>4</v>
       </c>
       <c r="G9" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$70,A9,主题清单!$J$2:$J$70,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$80,A9,主题清单!$J$2:$J$80,"已制作")</f>
         <v>3</v>
       </c>
       <c r="H9" s="2" t="n">
@@ -13291,11 +15402,11 @@
         <v>41</v>
       </c>
       <c r="F10" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$70,A10)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$80,A10)</f>
         <v>8</v>
       </c>
       <c r="G10" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$70,A10,主题清单!$J$2:$J$70,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$80,A10,主题清单!$J$2:$J$80,"已制作")</f>
         <v>7</v>
       </c>
       <c r="H10" s="2" t="n">
@@ -13320,11 +15431,11 @@
         <v>45</v>
       </c>
       <c r="F11" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$70,A11)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$80,A11)</f>
         <v>5</v>
       </c>
       <c r="G11" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$70,A11,主题清单!$J$2:$J$70,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$80,A11,主题清单!$J$2:$J$80,"已制作")</f>
         <v>4</v>
       </c>
       <c r="H11" s="2" t="n">
@@ -13349,11 +15460,11 @@
         <v>49</v>
       </c>
       <c r="F12" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$70,A12)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$80,A12)</f>
         <v>8</v>
       </c>
       <c r="G12" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$70,A12,主题清单!$J$2:$J$70,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$80,A12,主题清单!$J$2:$J$80,"已制作")</f>
         <v>8</v>
       </c>
       <c r="H12" s="2" t="n">
@@ -13378,11 +15489,11 @@
         <v>53</v>
       </c>
       <c r="F13" s="2" t="n">
-        <f aca="false">COUNTIF(主题清单!$B$2:$B$70,A13)</f>
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$80,A13)</f>
         <v>4</v>
       </c>
       <c r="G13" s="2" t="n">
-        <f aca="false">COUNTIFS(主题清单!$B$2:$B$70,A13,主题清单!$J$2:$J$70,"已制作")</f>
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$80,A13,主题清单!$J$2:$J$80,"已制作")</f>
         <v>4</v>
       </c>
       <c r="H13" s="2" t="n">
@@ -13390,30 +15501,88 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
+    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F14" s="8" t="n">
-        <f aca="false">SUM(F2:F13)</f>
-        <v>69</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <f aca="false">SUM(G2:G13)</f>
-        <v>63</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <f aca="false">SUM(H2:H13)</f>
+      <c r="B14" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$80,A14)</f>
+        <v>5</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$80,A14,主题清单!$J$2:$J$80,"已制作")</f>
+        <v>5</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <f aca="false">F14-G14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <f aca="false">COUNTIF(主题清单!$B$2:$B$80,A15)</f>
+        <v>5</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <f aca="false">COUNTIFS(主题清单!$B$2:$B$80,A15,主题清单!$J$2:$J$80,"已制作")</f>
+        <v>5</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <f aca="false">F15-G15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <f aca="false">SUM(F2:F15)</f>
+        <v>79</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <f aca="false">SUM(G2:G15)</f>
+        <v>73</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <f aca="false">SUM(H2:H15)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15" s="9" t="n">
-        <f aca="false">IF(F14=0,0,G14/F14)</f>
-        <v>0.91304347826087</v>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <f aca="false">IF(F16=0,0,G16/F16)</f>
+        <v>0.924050632911392</v>
       </c>
     </row>
   </sheetData>
@@ -13432,7 +15601,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N80"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -13452,7 +15621,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -13461,42 +15630,42 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>8</v>
@@ -13505,42 +15674,42 @@
         <v>9</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J2" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>8</v>
@@ -13549,42 +15718,42 @@
         <v>9</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="E3" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="I3" s="10" t="s">
         <v>81</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="J3" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="N3" s="10" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>8</v>
@@ -13593,19 +15762,19 @@
         <v>9</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="4" t="s">
@@ -13618,7 +15787,7 @@
     </row>
     <row r="5" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>8</v>
@@ -13627,40 +15796,40 @@
         <v>9</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>8</v>
@@ -13669,40 +15838,40 @@
         <v>9</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="N6" s="10" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>8</v>
@@ -13711,40 +15880,40 @@
         <v>9</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="N7" s="10" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>13</v>
@@ -13753,42 +15922,42 @@
         <v>14</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J8" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>13</v>
@@ -13797,42 +15966,42 @@
         <v>14</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J9" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="N9" s="10" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>13</v>
@@ -13841,40 +16010,40 @@
         <v>14</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I10" s="10"/>
       <c r="J10" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="N10" s="10" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>13</v>
@@ -13883,40 +16052,40 @@
         <v>14</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I11" s="10"/>
       <c r="J11" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>13</v>
@@ -13925,40 +16094,40 @@
         <v>14</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I12" s="10"/>
       <c r="J12" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="N12" s="10" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>13</v>
@@ -13967,40 +16136,40 @@
         <v>14</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I13" s="10"/>
       <c r="J13" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>18</v>
@@ -14009,42 +16178,42 @@
         <v>14</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="N14" s="10" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>18</v>
@@ -14053,42 +16222,42 @@
         <v>14</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J15" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>18</v>
@@ -14097,42 +16266,42 @@
         <v>14</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="G16" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="N16" s="10" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>18</v>
@@ -14141,40 +16310,40 @@
         <v>14</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="G17" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I17" s="10"/>
       <c r="J17" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>18</v>
@@ -14183,40 +16352,40 @@
         <v>14</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I18" s="10"/>
       <c r="J18" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="N18" s="10" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>18</v>
@@ -14225,40 +16394,40 @@
         <v>14</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="G19" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="I19" s="10"/>
       <c r="J19" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>22</v>
@@ -14267,42 +16436,42 @@
         <v>14</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="G20" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>22</v>
@@ -14311,40 +16480,40 @@
         <v>14</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B22" s="10" t="s">
         <v>22</v>
@@ -14353,40 +16522,40 @@
         <v>14</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="G22" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I22" s="10"/>
       <c r="J22" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="N22" s="10" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>22</v>
@@ -14395,40 +16564,40 @@
         <v>14</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="G23" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I23" s="10"/>
       <c r="J23" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>22</v>
@@ -14437,40 +16606,40 @@
         <v>14</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I24" s="10"/>
       <c r="J24" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="N24" s="10" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>25</v>
@@ -14479,42 +16648,42 @@
         <v>26</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J25" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>25</v>
@@ -14523,42 +16692,42 @@
         <v>26</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J26" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M26" s="10" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="N26" s="10" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>25</v>
@@ -14567,40 +16736,40 @@
         <v>26</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="G27" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B28" s="10" t="s">
         <v>25</v>
@@ -14609,40 +16778,40 @@
         <v>26</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I28" s="10"/>
       <c r="J28" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="M28" s="10" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="N28" s="10" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>25</v>
@@ -14651,19 +16820,19 @@
         <v>26</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>48</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="4" t="s">
@@ -14676,7 +16845,7 @@
     </row>
     <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>25</v>
@@ -14685,40 +16854,40 @@
         <v>26</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I30" s="10"/>
       <c r="J30" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="M30" s="10" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="N30" s="10" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>29</v>
@@ -14727,42 +16896,42 @@
         <v>26</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J31" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="M31" s="10" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>29</v>
@@ -14771,42 +16940,42 @@
         <v>26</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J32" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="M32" s="10" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="N32" s="10" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>29</v>
@@ -14815,40 +16984,40 @@
         <v>26</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="G33" s="11" t="s">
         <v>48</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I33" s="10"/>
       <c r="J33" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>29</v>
@@ -14857,40 +17026,40 @@
         <v>26</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I34" s="10"/>
       <c r="J34" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L34" s="11" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="M34" s="10" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="N34" s="10" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>29</v>
@@ -14899,40 +17068,40 @@
         <v>26</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="G35" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I35" s="10"/>
       <c r="J35" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="L35" s="11" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="M35" s="10" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>29</v>
@@ -14941,40 +17110,40 @@
         <v>26</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="G36" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I36" s="10"/>
       <c r="J36" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K36" s="11" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L36" s="11" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="M36" s="10" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="N36" s="10" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>33</v>
@@ -14983,42 +17152,42 @@
         <v>9</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J37" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="L37" s="11" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="M37" s="10" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>33</v>
@@ -15027,42 +17196,42 @@
         <v>9</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J38" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K38" s="11" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="L38" s="11" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="M38" s="10" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="N38" s="10" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B39" s="10" t="s">
         <v>33</v>
@@ -15071,40 +17240,40 @@
         <v>9</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K39" s="11" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="L39" s="11" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="M39" s="10" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>33</v>
@@ -15113,19 +17282,19 @@
         <v>9</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>48</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I40" s="2"/>
       <c r="J40" s="4" t="s">
@@ -15138,7 +17307,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>33</v>
@@ -15147,40 +17316,40 @@
         <v>9</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="L41" s="11" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="M41" s="10" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>36</v>
@@ -15189,42 +17358,42 @@
         <v>9</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G42" s="11" t="s">
         <v>48</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J42" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K42" s="11" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="L42" s="11" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="M42" s="10" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="N42" s="10" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>36</v>
@@ -15233,42 +17402,42 @@
         <v>9</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J43" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K43" s="11" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="L43" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="M43" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="M43" s="10" t="s">
-        <v>98</v>
-      </c>
       <c r="N43" s="10" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>36</v>
@@ -15277,19 +17446,19 @@
         <v>9</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>48</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I44" s="2"/>
       <c r="J44" s="4" t="s">
@@ -15302,7 +17471,7 @@
     </row>
     <row r="45" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>36</v>
@@ -15311,40 +17480,40 @@
         <v>9</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="G45" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I45" s="10"/>
       <c r="J45" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K45" s="11" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L45" s="11" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="M45" s="10" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>39</v>
@@ -15353,42 +17522,42 @@
         <v>9</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J46" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K46" s="11" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="L46" s="11" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="M46" s="10" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="N46" s="10" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>39</v>
@@ -15397,40 +17566,40 @@
         <v>9</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I47" s="10"/>
       <c r="J47" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K47" s="11" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="L47" s="11" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="M47" s="10" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>39</v>
@@ -15439,19 +17608,19 @@
         <v>9</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I48" s="2"/>
       <c r="J48" s="4" t="s">
@@ -15464,7 +17633,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>39</v>
@@ -15473,40 +17642,40 @@
         <v>9</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K49" s="11" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L49" s="11" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M49" s="10" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>39</v>
@@ -15515,40 +17684,40 @@
         <v>9</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="G50" s="11" t="s">
         <v>48</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I50" s="10"/>
       <c r="J50" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K50" s="11" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L50" s="11" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="M50" s="10" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="N50" s="10" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>39</v>
@@ -15557,40 +17726,40 @@
         <v>9</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K51" s="11" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L51" s="11" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="M51" s="10" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>39</v>
@@ -15599,40 +17768,40 @@
         <v>9</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="G52" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I52" s="10"/>
       <c r="J52" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K52" s="11" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L52" s="11" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="M52" s="10" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="N52" s="10" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B53" s="10" t="s">
         <v>39</v>
@@ -15641,40 +17810,40 @@
         <v>9</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="G53" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K53" s="11" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="L53" s="11" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="M53" s="10" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="B54" s="10" t="s">
         <v>42</v>
@@ -15683,42 +17852,42 @@
         <v>26</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J54" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K54" s="11" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="L54" s="11" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="M54" s="10" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="N54" s="10" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>42</v>
@@ -15727,42 +17896,42 @@
         <v>26</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="G55" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J55" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K55" s="11" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="L55" s="11" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="M55" s="10" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>42</v>
@@ -15771,40 +17940,40 @@
         <v>26</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="G56" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I56" s="10"/>
       <c r="J56" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K56" s="11" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="L56" s="11" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="M56" s="10" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="N56" s="10" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>42</v>
@@ -15813,19 +17982,19 @@
         <v>26</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I57" s="2"/>
       <c r="J57" s="4" t="s">
@@ -15838,7 +18007,7 @@
     </row>
     <row r="58" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B58" s="10" t="s">
         <v>42</v>
@@ -15847,40 +18016,40 @@
         <v>26</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="G58" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I58" s="10"/>
       <c r="J58" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K58" s="11" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="L58" s="11" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="M58" s="10" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="N58" s="10" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="10" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="B59" s="10" t="s">
         <v>46</v>
@@ -15889,42 +18058,42 @@
         <v>26</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="G59" s="11" t="s">
         <v>48</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J59" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K59" s="11" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="L59" s="11" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="M59" s="10" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="B60" s="10" t="s">
         <v>46</v>
@@ -15933,42 +18102,42 @@
         <v>26</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="G60" s="11" t="s">
         <v>48</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J60" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K60" s="11" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="L60" s="11" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="M60" s="10" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="N60" s="10" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="10" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="B61" s="10" t="s">
         <v>46</v>
@@ -15977,40 +18146,40 @@
         <v>26</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="G61" s="11" t="s">
         <v>48</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K61" s="11" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L61" s="11" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="M61" s="10" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="10" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="B62" s="10" t="s">
         <v>46</v>
@@ -16019,40 +18188,40 @@
         <v>26</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="G62" s="11" t="s">
         <v>48</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I62" s="10"/>
       <c r="J62" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K62" s="11" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L62" s="11" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="M62" s="10" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="N62" s="10" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="B63" s="10" t="s">
         <v>46</v>
@@ -16061,40 +18230,40 @@
         <v>26</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="G63" s="11" t="s">
         <v>48</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K63" s="11" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L63" s="11" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="M63" s="10" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="B64" s="10" t="s">
         <v>46</v>
@@ -16103,40 +18272,40 @@
         <v>26</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="G64" s="11" t="s">
         <v>48</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I64" s="10"/>
       <c r="J64" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K64" s="11" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L64" s="11" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="M64" s="10" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="N64" s="10" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="B65" s="10" t="s">
         <v>46</v>
@@ -16145,40 +18314,40 @@
         <v>26</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="G65" s="11" t="s">
         <v>48</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I65" s="10"/>
       <c r="J65" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K65" s="11" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L65" s="11" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="M65" s="10" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="10" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="B66" s="10" t="s">
         <v>46</v>
@@ -16187,40 +18356,40 @@
         <v>26</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="G66" s="11" t="s">
         <v>48</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I66" s="10"/>
       <c r="J66" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K66" s="11" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L66" s="11" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="M66" s="10" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="N66" s="10" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="B67" s="10" t="s">
         <v>50</v>
@@ -16229,42 +18398,42 @@
         <v>26</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="G67" s="11" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J67" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K67" s="11" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="L67" s="11" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="M67" s="10" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="10" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="B68" s="10" t="s">
         <v>50</v>
@@ -16273,42 +18442,42 @@
         <v>26</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H68" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J68" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K68" s="11" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="L68" s="11" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="M68" s="10" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="N68" s="10" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="B69" s="10" t="s">
         <v>50</v>
@@ -16317,40 +18486,40 @@
         <v>26</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K69" s="11" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="L69" s="11" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="M69" s="10" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="10" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="B70" s="10" t="s">
         <v>50</v>
@@ -16359,39 +18528,459 @@
         <v>26</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="G70" s="11" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="H70" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I70" s="10"/>
       <c r="J70" s="11" t="s">
         <v>6</v>
       </c>
       <c r="K70" s="11" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="L70" s="11" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="M70" s="10" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="N70" s="10" t="s">
-        <v>457</v>
+        <v>464</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="F71" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="G71" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H71" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I71" s="10"/>
+      <c r="J71" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K71" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="L71" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="M71" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="N71" s="10" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>472</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="F72" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="G72" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H72" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I72" s="10"/>
+      <c r="J72" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K72" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="L72" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="M72" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="N72" s="10" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="F73" s="11" t="s">
+        <v>479</v>
+      </c>
+      <c r="G73" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H73" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I73" s="10"/>
+      <c r="J73" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K73" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="L73" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="M73" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="N73" s="10" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>482</v>
+      </c>
+      <c r="E74" s="11" t="s">
+        <v>483</v>
+      </c>
+      <c r="F74" s="11" t="s">
+        <v>484</v>
+      </c>
+      <c r="G74" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H74" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I74" s="10"/>
+      <c r="J74" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K74" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="L74" s="11" t="s">
+        <v>485</v>
+      </c>
+      <c r="M74" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="N74" s="10" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="10" t="s">
+        <v>487</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>488</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="F75" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="G75" s="11" t="s">
+        <v>448</v>
+      </c>
+      <c r="H75" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I75" s="10"/>
+      <c r="J75" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K75" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="L75" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="M75" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="N75" s="10" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>493</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="F76" s="11" t="s">
+        <v>495</v>
+      </c>
+      <c r="G76" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H76" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I76" s="10"/>
+      <c r="J76" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K76" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="L76" s="11" t="s">
+        <v>496</v>
+      </c>
+      <c r="M76" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="N76" s="10" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="B77" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D77" s="11" t="s">
+        <v>499</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="F77" s="11" t="s">
+        <v>501</v>
+      </c>
+      <c r="G77" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I77" s="10"/>
+      <c r="J77" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K77" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="L77" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="M77" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="N77" s="10" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="B78" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D78" s="11" t="s">
+        <v>504</v>
+      </c>
+      <c r="E78" s="11" t="s">
+        <v>505</v>
+      </c>
+      <c r="F78" s="11" t="s">
+        <v>506</v>
+      </c>
+      <c r="G78" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H78" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I78" s="10"/>
+      <c r="J78" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K78" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="L78" s="11" t="s">
+        <v>496</v>
+      </c>
+      <c r="M78" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="N78" s="10" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="10" t="s">
+        <v>508</v>
+      </c>
+      <c r="B79" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="E79" s="11" t="s">
+        <v>510</v>
+      </c>
+      <c r="F79" s="11" t="s">
+        <v>511</v>
+      </c>
+      <c r="G79" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H79" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I79" s="10"/>
+      <c r="J79" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K79" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="L79" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="M79" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="N79" s="10" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="10" t="s">
+        <v>513</v>
+      </c>
+      <c r="B80" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>515</v>
+      </c>
+      <c r="F80" s="11" t="s">
+        <v>516</v>
+      </c>
+      <c r="G80" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H80" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I80" s="10"/>
+      <c r="J80" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K80" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="L80" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="M80" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="N80" s="10" t="s">
+        <v>517</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N70"/>
+  <autoFilter ref="A1:N80"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -16415,12 +19004,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="90"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>458</v>
+        <v>518</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>459</v>
+        <v>519</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16428,63 +19017,63 @@
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>460</v>
+        <v>520</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>461</v>
+        <v>521</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>462</v>
+        <v>522</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>463</v>
+        <v>523</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>464</v>
+        <v>524</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>465</v>
+        <v>525</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>466</v>
+        <v>526</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>467</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>468</v>
+        <v>528</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>469</v>
+        <v>529</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>470</v>
+        <v>530</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>471</v>
+        <v>531</v>
       </c>
     </row>
   </sheetData>
